--- a/files/BA.xlsx
+++ b/files/BA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\yanagiha.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2716C694-2DB3-4D08-8828-C05BA0B477EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AE773D-B1EB-470F-8ACB-B7A2D6AD112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程（国服）" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1621">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7782,6 +7782,23 @@
   <si>
     <t>为期5天
 感谢猫猫老公的代打！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桔梗（A），水花子，小夏，红薯。亚子，妃咲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红薯，野宫，小夏，斯大萝。亚子，妃咲
+大瞬，纯子，水星野，小桃。otto，春锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忧，红薯，枪星，春佳。亚子，妃咲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢猫猫的蓝甲紫甲的代打！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -25062,7 +25079,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" ht="27.6">
       <c r="A99" s="194">
         <v>46089</v>
       </c>
@@ -25075,10 +25092,20 @@
       <c r="D99" s="193" t="s">
         <v>196</v>
       </c>
-      <c r="E99" s="193"/>
-      <c r="F99" s="193"/>
+      <c r="E99" s="193" t="s">
+        <v>211</v>
+      </c>
+      <c r="F99" s="193">
+        <v>2253</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="H99" s="1" t="s">
         <v>1539</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>1618</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -25088,8 +25115,17 @@
       <c r="D100" s="193"/>
       <c r="E100" s="193"/>
       <c r="F100" s="193"/>
+      <c r="G100" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="H100" s="1" t="s">
         <v>1540</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>1620</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -25099,8 +25135,14 @@
       <c r="D101" s="193"/>
       <c r="E101" s="193"/>
       <c r="F101" s="193"/>
+      <c r="G101" s="1" t="s">
+        <v>455</v>
+      </c>
       <c r="H101" s="1" t="s">
         <v>1568</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>1617</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>1603</v>
